--- a/exports/relatorio_lancamentos_17_07_2026.xlsx
+++ b/exports/relatorio_lancamentos_17_07_2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Relatorio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relatorio'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Relatorio'!$A$1:$I$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -494,17 +494,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KGGUCV7</t>
+          <t>KGA3AB0</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MARCELO SAHADE</t>
+          <t>ELIANE APARECIDA GUIDOTTI MIRANDA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>EAGM</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -515,10 +515,208 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>17/07/2026 21:22:33</t>
+          <t>17/07/2026 23:01:12</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>evolucao
+Dados da Internação - Caráter da internação *
+Dados da Internação - Tipo da internação *
+Dados da Internação - Data da internação *
+Dados da Internação - Acomodação *
+Dados da Internação - Paciente em isolamento? *
+Dados da Internação - Queixa *
+Dados da Internação - CID de internação *
+Dados da Internação - CID ajustado *
+Dados da Internação - Comorbidades *
+Dados da Internação - Tempo de existência da doença *
+Dados da Internação - Nomenclatura do tempo de existência da doença *
+Exame Físico - Estado geral *
+Exame Físico - PA Sistólica max (mmHg) *
+Exame Físico - PA Diastólica max (mmHg) *
+Exame Físico - FC máx. (bpm) *
+Exame Físico - FR máx. (irpm) *
+Exame Físico - SpO2 mín. (%) *
+Exame Físico - Temperatura máx. (°C) *
+Exame Físico - Nível de consciência *
+Exame Físico - Mobilidade e dependência *
+Exame Físico - Acesso venoso? *
+Exame Físico - Qual o acesso venoso? * (cond.)
+Exame Físico - Via respiratória *
+Exame Físico - Suporte respiratório *
+Exame Físico - Alimentação *
+Exame Físico - Lesões na pele? *
+Exame Físico - Controle de eliminação *
+UTI - 1. Abertura Ocular (E) - Selecione a melhor resposta observada. *
+UTI - 2. Resposta Verbal (V) - Avaliar conteúdo da comunicação verbal. *
+UTI - 3. Melhor Resposta Motora (M) - Registrar a melhor resposta obtida. *
+UTI - 4. Resposta Pupilar (P) - Avaliar reatividade pupilar ao estímulo luminoso. *
+UTI - Monitorização *
+UTI - Uso de droga vasoativa? *
+Conduta Clínica - Uso de antibiótico? *
+Conduta Clínica - Uso de antifúngico? *
+Conduta Clínica - Uso de antiviral? *
+Conduta Clínica - Câmara Hiperbárica * (cond.)
+Conduta Clínica - Administração de Imunoglobulina *
+Conduta Clínica - Terapias Ativas (ex .: fisioterapia, suporte clínico) * *
+Conduta Clínica - Realizado procedimento cirúrgico? *
+Condição Adquirida - Paciente adquiriu alguma condição? *
+Parecer do Auditor - Pertinência Técnica da Internação *
+Parecer do Auditor - Pertinência Técnica da permanência hospitalar *
+Parecer do Auditor - Paciente permanece internado? *
+Parecer do Auditor - Selecione o desfecho assistencial * (cond.)
+Parecer do Auditor - Data do desfecho * (cond.)
+Parecer do Auditor - Hora do desfecho * (cond.)
+Parecer do Auditor - Programação de alta * (cond.)
+Lançamento Salus - Status
+Lançamento Salus - Data/hora
+Lançamento Salus - Mensagem
+Lançamento Salus - URL</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Dados da Internação - Motivo do isolamento * (cond.)
+Exame Físico - Detalhamento do acesso central * (cond.)
+Exame Físico - Tipo de aspiração * (cond.)
+Exame Físico - Detalhamento do suporte respiratório * (cond.)
+Exame Físico - Frequência do suporte respiratório * (cond.)
+Exame Físico - Detalhamento enteral * (cond.)
+Exame Físico - Localização da lesão * (cond.)
+Exame Físico - Detalhamento trocantérica * (cond.)
+Exame Físico - Detalhamento calcâneo * (cond.)
+Exame Físico - Localização outras regiões * (cond.)
+Exame Físico - Tipo de lesão identificada * (cond.)
+Exame Físico - Condição atual da lesão * (cond.)
+Exame Físico - Características clínicas da lesão * (cond.)
+Exame Físico - Houve curativo? * (cond.)
+Exame Físico - Tipo de curativo * (cond.)
+Exame Físico - Frequência de troca do curativo * (cond.)
+Exame Físico - Frequência da troca do curativo está adequada? * (cond.)
+UTI - Tipo de monitorização * (cond.)
+UTI - Drogas vasoativas em uso * (cond.)
+UTI - Creatinina sérica (mg/dL) *
+UTI - Não mensurado * (cond.)
+UTI - pH arterial *
+UTI - Não mensurado * (cond.) [2]
+UTI - PaO2 (mmHg) *
+UTI - Não mensurado * (cond.) [3]
+UTI - FiO2 (%) *
+UTI - Não mensurado * (cond.) [4]
+UTI - Categoria do diagnóstico principal *
+Conduta Clínica - Selecione os antibióticos em uso * (cond.)
+Conduta Clínica - Antibiótico selecionado * (cond.)
+Conduta Clínica - Dosagem do antibiótico * (cond.)
+Conduta Clínica - Via do antibiótico * (cond.)
+Conduta Clínica - Selecione os antifúngicos em uso * (cond.)
+Conduta Clínica - Antifúngico selecionado * (cond.)
+Conduta Clínica - Via do antifúngico * (cond.)
+Conduta Clínica - Selecione os antivirais em uso * (cond.)
+Conduta Clínica - Antiviral selecionado * (cond.)
+Conduta Clínica - Via do antiviral * (cond.)
+Conduta Clínica - Terapias em andamento * (cond.)
+Conduta Clínica - Tipo de terapia renal substitutiva (TRS) * (cond.)
+Conduta Clínica - Tipo de Quimioterapia * (cond.)
+Conduta Clínica - Tipo de Quimioterapia curativa * (cond.)
+Conduta Clínica - Tipo de radioterapia * (cond.)
+Conduta Clínica - TUSS + Nome do Procedimento * (cond.)
+Conduta Clínica - Quantidade Solicitada * (cond.)
+Conduta Clínica - Quantidade Autorizada * (cond.)
+Conduta Clínica - Quantidade Realizada * (cond.)
+Conduta Clínica - Anvisa + Nome do OPME (cond.)
+Conduta Clínica - Quantidade Solicitada (cond.)
+Conduta Clínica - Quantidade Autorizada (cond.)
+Conduta Clínica - Quantidade Utilizada (cond.)
+Conduta Clínica - Tipo de anestesia * (cond.)
+Conduta Clínica - Houve intercorrências no intraoperatório? * (cond.)
+Conduta Clínica - Tipo de intercorrência * (cond.)
+Conduta Clínica - Justifique * (cond.)
+Condição Adquirida - Condição adquirida * (cond.)
+Condição Adquirida - Caracterização clínica da condição * (cond.)
+Condição Adquirida - Data da condição adquirida * (cond.)
+Condição Adquirida - Caracterização clínica da condição * (cond.) [2]
+Condição Adquirida - Data da condição adquirida * (cond.) [2]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [3]
+Condição Adquirida - Data da condição adquirida * (cond.) [3]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [4]
+Condição Adquirida - Data da condição adquirida * (cond.) [4]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [5]
+Condição Adquirida - Data da condição adquirida * (cond.) [5]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [6]
+Condição Adquirida - Data da condição adquirida * (cond.) [6]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [7]
+Condição Adquirida - Data da condição adquirida * (cond.) [7]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [8]
+Condição Adquirida - Data da condição adquirida * (cond.) [8]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [9]
+Condição Adquirida - Data da condição adquirida * (cond.) [9]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [10]
+Condição Adquirida - Data da condição adquirida * (cond.) [10]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [11]
+Condição Adquirida - Data da condição adquirida * (cond.) [11]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [12]
+Condição Adquirida - Data da condição adquirida * (cond.) [12]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [13]
+Condição Adquirida - Data da condição adquirida * (cond.) [13]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [14]
+Condição Adquirida - Data da condição adquirida * (cond.) [14]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [15]
+Condição Adquirida - Data da condição adquirida * (cond.) [15]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [16]
+Condição Adquirida - Data da condição adquirida * (cond.) [16]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [17]
+Condição Adquirida - Data da condição adquirida * (cond.) [17]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [18]
+Condição Adquirida - Data da condição adquirida * (cond.) [18]
+Condição Adquirida - Caracterização clínica da condição - Outros (cond.)
+Parecer do Auditor - Mostrar histórico de prorrogação
+Parecer do Auditor - Prorrogação
+Parecer do Auditor - Datas * (cond.)
+Parecer do Auditor - Acomodação utilizada * (cond.)
+Parecer do Auditor - Recomendação * (cond.)
+Parecer do Auditor - Parecer * (cond.)
+Parecer do Auditor - Interlocutor * (cond.)
+Parecer do Auditor - Nome * (cond.)
+Parecer do Auditor - Status * (cond.)
+Parecer do Auditor - Pendências da operadora (cond.)
+Parecer do Auditor - Justifique * (cond.)
+Parecer do Auditor - Pendências do hospital (cond.)
+Parecer do Auditor - Justifique * (cond.) [2]
+Parecer do Auditor - Transição de cuidados (cond.)
+Parecer do Auditor - Justifique * (cond.) [3]</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>KGGKU74</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>MARIA DAS GRACAS LUCHESI ZABANI</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>MDGLZ</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:01:12</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>evolucao
 Dados da Internação - Comorbidades *
@@ -552,10 +750,13 @@
 Parecer do Auditor - Selecione o desfecho assistencial * (cond.)
 Parecer do Auditor - Data do desfecho * (cond.)
 Parecer do Auditor - Hora do desfecho * (cond.)
-Parecer do Auditor - Programação de alta * (cond.)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+Parecer do Auditor - Programação de alta * (cond.)
+Lançamento Salus - Status
+Lançamento Salus - Data/hora
+Lançamento Salus - Mensagem</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Dados da Internação - Caráter da internação *
 Dados da Internação - Tipo da internação *
@@ -681,47 +882,188 @@
 Parecer do Auditor - Justifique * (cond.) [2]
 Parecer do Auditor - Transição de cuidados (cond.)
 Parecer do Auditor - Justifique * (cond.) [3]
-Lançamento Salus - Status
-Lançamento Salus - Data/hora
-Lançamento Salus - Mensagem
 Lançamento Salus - URL</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>KG3YAK0</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WILSON CRUZ</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>WC</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>KGKRMR3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>MAURICIO BUSATO</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ERRO</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Comorbidade Z72.0 não persistiu no HTML: {'ok': False, 'error': 'opção não encontrada'}</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>17/07/2026 21:22:33</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Página Conduta Clínica não ficou verde; lote interrompido neste paciente.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:01:12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Dados da Internação - Motivo do isolamento * (cond.)
+Exame Físico - Tipo de aspiração * (cond.)
+Exame Físico - Detalhamento do suporte respiratório * (cond.)
+Exame Físico - Frequência do suporte respiratório * (cond.)
+Exame Físico - Detalhamento enteral * (cond.)
+Exame Físico - Localização da lesão * (cond.)
+Exame Físico - Detalhamento trocantérica * (cond.)
+Exame Físico - Detalhamento calcâneo * (cond.)
+Exame Físico - Localização outras regiões * (cond.)
+Exame Físico - Tipo de lesão identificada * (cond.)
+Exame Físico - Condição atual da lesão * (cond.)
+Exame Físico - Características clínicas da lesão * (cond.)
+Exame Físico - Houve curativo? * (cond.)
+Exame Físico - Tipo de curativo * (cond.)
+Exame Físico - Frequência de troca do curativo * (cond.)
+Exame Físico - Frequência da troca do curativo está adequada? * (cond.)
+UTI - Tipo de monitorização * (cond.)
+UTI - Drogas vasoativas em uso * (cond.)
+UTI - Não mensurado * (cond.)
+UTI - pH arterial *
+UTI - PaO2 (mmHg) *
+UTI - FiO2 (%) *
+Conduta Clínica - Antibiótico selecionado * (cond.)
+Conduta Clínica - Dosagem do antibiótico * (cond.)
+Conduta Clínica - Via do antibiótico * (cond.)
+Conduta Clínica - Selecione os antifúngicos em uso * (cond.)
+Conduta Clínica - Antifúngico selecionado * (cond.)
+Conduta Clínica - Via do antifúngico * (cond.)
+Conduta Clínica - Selecione os antivirais em uso * (cond.)
+Conduta Clínica - Antiviral selecionado * (cond.)
+Conduta Clínica - Via do antiviral * (cond.)
+Conduta Clínica - Tipo de terapia renal substitutiva (TRS) * (cond.)
+Conduta Clínica - Tipo de radioterapia * (cond.)
+Conduta Clínica - TUSS + Nome do Procedimento * (cond.)
+Conduta Clínica - Quantidade Solicitada * (cond.)
+Conduta Clínica - Quantidade Autorizada * (cond.)
+Conduta Clínica - Quantidade Realizada * (cond.)
+Conduta Clínica - Anvisa + Nome do OPME (cond.)
+Conduta Clínica - Quantidade Solicitada (cond.)
+Conduta Clínica - Quantidade Autorizada (cond.)
+Conduta Clínica - Quantidade Utilizada (cond.)
+Conduta Clínica - Tipo de anestesia * (cond.)
+Conduta Clínica - Houve intercorrências no intraoperatório? * (cond.)
+Conduta Clínica - Tipo de intercorrência * (cond.)
+Conduta Clínica - Justifique * (cond.)
+Condição Adquirida - Condição adquirida * (cond.)
+Condição Adquirida - Caracterização clínica da condição * (cond.)
+Condição Adquirida - Data da condição adquirida * (cond.)
+Condição Adquirida - Caracterização clínica da condição * (cond.) [2]
+Condição Adquirida - Data da condição adquirida * (cond.) [2]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [3]
+Condição Adquirida - Data da condição adquirida * (cond.) [3]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [4]
+Condição Adquirida - Data da condição adquirida * (cond.) [4]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [5]
+Condição Adquirida - Data da condição adquirida * (cond.) [5]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [6]
+Condição Adquirida - Data da condição adquirida * (cond.) [6]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [7]
+Condição Adquirida - Data da condição adquirida * (cond.) [7]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [8]
+Condição Adquirida - Data da condição adquirida * (cond.) [8]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [9]
+Condição Adquirida - Data da condição adquirida * (cond.) [9]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [10]
+Condição Adquirida - Data da condição adquirida * (cond.) [10]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [11]
+Condição Adquirida - Data da condição adquirida * (cond.) [11]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [12]
+Condição Adquirida - Data da condição adquirida * (cond.) [12]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [13]
+Condição Adquirida - Data da condição adquirida * (cond.) [13]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [14]
+Condição Adquirida - Data da condição adquirida * (cond.) [14]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [15]
+Condição Adquirida - Data da condição adquirida * (cond.) [15]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [16]
+Condição Adquirida - Data da condição adquirida * (cond.) [16]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [17]
+Condição Adquirida - Data da condição adquirida * (cond.) [17]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [18]
+Condição Adquirida - Data da condição adquirida * (cond.) [18]
+Condição Adquirida - Caracterização clínica da condição - Outros (cond.)
+Parecer do Auditor - Selecione o desfecho assistencial * (cond.)
+Parecer do Auditor - Data do desfecho * (cond.)
+Parecer do Auditor - Hora do desfecho * (cond.)
+Parecer do Auditor - Mostrar histórico de prorrogação
+Parecer do Auditor - Prorrogação
+Parecer do Auditor - Datas * (cond.)
+Parecer do Auditor - Acomodação utilizada * (cond.)
+Parecer do Auditor - Recomendação * (cond.)
+Parecer do Auditor - Parecer * (cond.)
+Parecer do Auditor - Interlocutor * (cond.)
+Parecer do Auditor - Nome * (cond.)
+Parecer do Auditor - Status * (cond.)
+Parecer do Auditor - Pendências da operadora (cond.)
+Parecer do Auditor - Justifique * (cond.)
+Parecer do Auditor - Pendências do hospital (cond.)
+Parecer do Auditor - Justifique * (cond.) [2]
+Parecer do Auditor - Transição de cuidados (cond.)
+Parecer do Auditor - Justifique * (cond.) [3]
+Lançamento Salus - URL</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Página Conduta Clínica não ficou verde; lote interrompido neste paciente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>KG7WZM0</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BRIGITTE ADELINA MELCHER</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>BAM</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:01:12</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dados da Internação - Caráter da internação *
 Dados da Internação - Tipo da internação *
@@ -732,12 +1074,14 @@
 Dados da Internação - Queixa *
 Dados da Internação - CID de internação *
 Dados da Internação - CID ajustado *
+Exame Físico - PA Sistólica max (mmHg) *
+Exame Físico - PA Diastólica max (mmHg) *
+Exame Físico - FC máx. (bpm) *
 Exame Físico - FR máx. (irpm) *
 Exame Físico - SpO2 mín. (%) *
 Exame Físico - Temperatura máx. (°C) *
 Exame Físico - Detalhamento do acesso central * (cond.)
 Exame Físico - Tipo de aspiração * (cond.)
-Exame Físico - Detalhamento do suporte respiratório * (cond.)
 Exame Físico - Frequência do suporte respiratório * (cond.)
 Exame Físico - Detalhamento enteral * (cond.)
 Exame Físico - Localização da lesão * (cond.)
@@ -828,9 +1172,6 @@
 Condição Adquirida - Caracterização clínica da condição * (cond.) [18]
 Condição Adquirida - Data da condição adquirida * (cond.) [18]
 Condição Adquirida - Caracterização clínica da condição - Outros (cond.)
-Parecer do Auditor - Selecione o desfecho assistencial * (cond.)
-Parecer do Auditor - Data do desfecho * (cond.)
-Parecer do Auditor - Hora do desfecho * (cond.)
 Parecer do Auditor - Mostrar histórico de prorrogação
 Parecer do Auditor - Prorrogação
 Parecer do Auditor - Datas * (cond.)
@@ -846,20 +1187,180 @@
 Parecer do Auditor - Justifique * (cond.) [2]
 Parecer do Auditor - Transição de cuidados (cond.)
 Parecer do Auditor - Justifique * (cond.) [3]
-Lançamento Salus - Status
-Lançamento Salus - Data/hora
-Lançamento Salus - Mensagem
 Lançamento Salus - URL</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Comorbidade Z72.0 não persistiu no HTML: {'ok': False, 'error': 'opção não encontrada'}</t>
+      <c r="I5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>KG7WP87</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>DENISE REI PASSOS CAMPOS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DRPC</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Secao 100002 nao carregou a tela esperada (Exame Físico).</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:01:12</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Dados da Internação - Caráter da internação *
+Dados da Internação - Tipo da internação *
+Dados da Internação - Data da internação *
+Dados da Internação - Acomodação *
+Dados da Internação - Paciente em isolamento? *
+Dados da Internação - Motivo do isolamento * (cond.)
+Dados da Internação - Queixa *
+Dados da Internação - CID de internação *
+Dados da Internação - CID ajustado *
+Exame Físico - PA Sistólica max (mmHg) *
+Exame Físico - PA Diastólica max (mmHg) *
+Exame Físico - FC máx. (bpm) *
+Exame Físico - FR máx. (irpm) *
+Exame Físico - SpO2 mín. (%) *
+Exame Físico - Temperatura máx. (°C) *
+Exame Físico - Detalhamento do acesso central * (cond.)
+Exame Físico - Tipo de aspiração * (cond.)
+Exame Físico - Detalhamento do suporte respiratório * (cond.)
+Exame Físico - Frequência do suporte respiratório * (cond.)
+Exame Físico - Detalhamento enteral * (cond.)
+Exame Físico - Localização da lesão * (cond.)
+Exame Físico - Detalhamento trocantérica * (cond.)
+Exame Físico - Detalhamento calcâneo * (cond.)
+Exame Físico - Localização outras regiões * (cond.)
+Exame Físico - Tipo de lesão identificada * (cond.)
+Exame Físico - Condição atual da lesão * (cond.)
+Exame Físico - Características clínicas da lesão * (cond.)
+Exame Físico - Houve curativo? * (cond.)
+Exame Físico - Tipo de curativo * (cond.)
+Exame Físico - Frequência de troca do curativo * (cond.)
+Exame Físico - Frequência da troca do curativo está adequada? * (cond.)
+UTI - Monitorização *
+UTI - Tipo de monitorização * (cond.)
+UTI - Uso de droga vasoativa? *
+UTI - Drogas vasoativas em uso * (cond.)
+UTI - Creatinina sérica (mg/dL) *
+UTI - Não mensurado * (cond.)
+UTI - pH arterial *
+UTI - Não mensurado * (cond.) [2]
+UTI - PaO2 (mmHg) *
+UTI - Não mensurado * (cond.) [3]
+UTI - FiO2 (%) *
+UTI - Não mensurado * (cond.) [4]
+UTI - Categoria do diagnóstico principal *
+Conduta Clínica - Selecione os antibióticos em uso * (cond.)
+Conduta Clínica - Antibiótico selecionado * (cond.)
+Conduta Clínica - Dosagem do antibiótico * (cond.)
+Conduta Clínica - Via do antibiótico * (cond.)
+Conduta Clínica - Selecione os antifúngicos em uso * (cond.)
+Conduta Clínica - Antifúngico selecionado * (cond.)
+Conduta Clínica - Via do antifúngico * (cond.)
+Conduta Clínica - Selecione os antivirais em uso * (cond.)
+Conduta Clínica - Antiviral selecionado * (cond.)
+Conduta Clínica - Via do antiviral * (cond.)
+Conduta Clínica - Terapias em andamento * (cond.)
+Conduta Clínica - Tipo de terapia renal substitutiva (TRS) * (cond.)
+Conduta Clínica - Tipo de Quimioterapia * (cond.)
+Conduta Clínica - Tipo de Quimioterapia curativa * (cond.)
+Conduta Clínica - Tipo de radioterapia * (cond.)
+Conduta Clínica - TUSS + Nome do Procedimento * (cond.)
+Conduta Clínica - Quantidade Solicitada * (cond.)
+Conduta Clínica - Quantidade Autorizada * (cond.)
+Conduta Clínica - Quantidade Realizada * (cond.)
+Conduta Clínica - Anvisa + Nome do OPME (cond.)
+Conduta Clínica - Quantidade Solicitada (cond.)
+Conduta Clínica - Quantidade Autorizada (cond.)
+Conduta Clínica - Quantidade Utilizada (cond.)
+Conduta Clínica - Tipo de anestesia * (cond.)
+Conduta Clínica - Houve intercorrências no intraoperatório? * (cond.)
+Conduta Clínica - Tipo de intercorrência * (cond.)
+Conduta Clínica - Justifique * (cond.)
+Condição Adquirida - Condição adquirida * (cond.)
+Condição Adquirida - Caracterização clínica da condição * (cond.)
+Condição Adquirida - Data da condição adquirida * (cond.)
+Condição Adquirida - Caracterização clínica da condição * (cond.) [2]
+Condição Adquirida - Data da condição adquirida * (cond.) [2]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [3]
+Condição Adquirida - Data da condição adquirida * (cond.) [3]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [4]
+Condição Adquirida - Data da condição adquirida * (cond.) [4]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [5]
+Condição Adquirida - Data da condição adquirida * (cond.) [5]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [6]
+Condição Adquirida - Data da condição adquirida * (cond.) [6]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [7]
+Condição Adquirida - Data da condição adquirida * (cond.) [7]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [8]
+Condição Adquirida - Data da condição adquirida * (cond.) [8]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [9]
+Condição Adquirida - Data da condição adquirida * (cond.) [9]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [10]
+Condição Adquirida - Data da condição adquirida * (cond.) [10]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [11]
+Condição Adquirida - Data da condição adquirida * (cond.) [11]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [12]
+Condição Adquirida - Data da condição adquirida * (cond.) [12]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [13]
+Condição Adquirida - Data da condição adquirida * (cond.) [13]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [14]
+Condição Adquirida - Data da condição adquirida * (cond.) [14]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [15]
+Condição Adquirida - Data da condição adquirida * (cond.) [15]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [16]
+Condição Adquirida - Data da condição adquirida * (cond.) [16]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [17]
+Condição Adquirida - Data da condição adquirida * (cond.) [17]
+Condição Adquirida - Caracterização clínica da condição * (cond.) [18]
+Condição Adquirida - Data da condição adquirida * (cond.) [18]
+Condição Adquirida - Caracterização clínica da condição - Outros (cond.)
+Parecer do Auditor - Mostrar histórico de prorrogação
+Parecer do Auditor - Prorrogação
+Parecer do Auditor - Datas * (cond.)
+Parecer do Auditor - Acomodação utilizada * (cond.)
+Parecer do Auditor - Recomendação * (cond.)
+Parecer do Auditor - Parecer * (cond.)
+Parecer do Auditor - Interlocutor * (cond.)
+Parecer do Auditor - Nome * (cond.)
+Parecer do Auditor - Status * (cond.)
+Parecer do Auditor - Pendências da operadora (cond.)
+Parecer do Auditor - Justifique * (cond.)
+Parecer do Auditor - Pendências do hospital (cond.)
+Parecer do Auditor - Justifique * (cond.) [2]
+Parecer do Auditor - Transição de cuidados (cond.)
+Parecer do Auditor - Justifique * (cond.) [3]
+Lançamento Salus - URL</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Secao 100002 nao carregou a tela esperada (Exame Físico).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>